--- a/data/trans_orig/P16A_n_R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>459095</t>
+          <t>458257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470884</t>
+          <t>470906</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294871</t>
+          <t>294775</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304592</t>
+          <t>304702</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758643</t>
+          <t>758217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773549</t>
+          <t>773350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359765</t>
+          <t>358707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366111</t>
+          <t>366109</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365465</t>
+          <t>365408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728488</t>
+          <t>728246</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737057</t>
+          <t>737042</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>22366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525957</t>
+          <t>528122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539001</t>
+          <t>538893</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156967</t>
+          <t>157950</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165884</t>
+          <t>165997</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>689251</t>
+          <t>687805</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>703024</t>
+          <t>703065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32045</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9586</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25097</t>
+          <t>25621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28651</t>
+          <t>27915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>52736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1206289</t>
+          <t>1205838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1224366</t>
+          <t>1224290</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689188</t>
+          <t>688664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>704699</t>
+          <t>704162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1900170</t>
+          <t>1899884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1923969</t>
+          <t>1924705</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>19997</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30130</t>
+          <t>29484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335732</t>
+          <t>335952</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346691</t>
+          <t>346665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>548717</t>
+          <t>548755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>562424</t>
+          <t>562652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>889177</t>
+          <t>889823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>907409</t>
+          <t>907278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>34040</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62154</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33555</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62178</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>298201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1186606</t>
+          <t>1188144</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1213250</t>
+          <t>1214720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1484782</t>
+          <t>1485759</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1513405</t>
+          <t>1512975</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>36510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63649</t>
+          <t>63511</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70791</t>
+          <t>68943</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>105674</t>
+          <t>106280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>115983</t>
+          <t>114070</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>161916</t>
+          <t>160359</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3206541</t>
+          <t>3206679</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3234666</t>
+          <t>3233680</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3272450</t>
+          <t>3271844</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3307333</t>
+          <t>3309181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6486398</t>
+          <t>6487955</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6532331</t>
+          <t>6534244</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24161</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>423695</t>
+          <t>424654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436208</t>
+          <t>436198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>299831</t>
+          <t>298515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311339</t>
+          <t>311335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727504</t>
+          <t>729201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745615</t>
+          <t>745675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>15212</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>400034</t>
+          <t>401559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415644</t>
+          <t>415573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322790</t>
+          <t>322799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>334119</t>
+          <t>334063</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729792</t>
+          <t>729945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747348</t>
+          <t>748517</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>31061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>16650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44174</t>
+          <t>41340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>596922</t>
+          <t>598354</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618712</t>
+          <t>618824</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243089</t>
+          <t>243479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255149</t>
+          <t>255909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>845370</t>
+          <t>848204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>870952</t>
+          <t>871103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>12768</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30536</t>
+          <t>30039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35192</t>
+          <t>35099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63251</t>
+          <t>61936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128473</t>
+          <t>1128970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146270</t>
+          <t>1146241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>727946</t>
+          <t>729758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>749045</t>
+          <t>749669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1862416</t>
+          <t>1863731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1890475</t>
+          <t>1890568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>17539</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32634</t>
+          <t>34954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60024</t>
+          <t>61956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42677</t>
+          <t>42471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72898</t>
+          <t>72549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>494044</t>
+          <t>493057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506193</t>
+          <t>506250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>701498</t>
+          <t>699566</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>728888</t>
+          <t>726568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1199220</t>
+          <t>1199569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1229441</t>
+          <t>1229647</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61536</t>
+          <t>61951</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>97233</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61515</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97678</t>
+          <t>97687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264956</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1011254</t>
+          <t>1012118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1047815</t>
+          <t>1047400</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1278555</t>
+          <t>1278546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1314718</t>
+          <t>1314556</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46208</t>
+          <t>45406</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83188</t>
+          <t>79910</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>151009</t>
+          <t>150147</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204937</t>
+          <t>205507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207464</t>
+          <t>205162</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>274241</t>
+          <t>271261</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3338722</t>
+          <t>3342000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3375702</t>
+          <t>3376504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3345188</t>
+          <t>3344618</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3399116</t>
+          <t>3399978</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6697794</t>
+          <t>6700774</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6764571</t>
+          <t>6766873</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14855</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11717</t>
+          <t>11657</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414237</t>
+          <t>414983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426485</t>
+          <t>426096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335338</t>
+          <t>335398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>345025</t>
+          <t>344978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>755280</t>
+          <t>756700</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>769721</t>
+          <t>770025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15807</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369592</t>
+          <t>370905</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359836</t>
+          <t>358879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370181</t>
+          <t>369413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733693</t>
+          <t>735605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746359</t>
+          <t>746514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12339</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18513</t>
+          <t>17405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24772</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509213</t>
+          <t>509575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519549</t>
+          <t>519866</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147610</t>
+          <t>148718</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161679</t>
+          <t>161583</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663264</t>
+          <t>663674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679738</t>
+          <t>679755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32334</t>
+          <t>32487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38018</t>
+          <t>37502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35440</t>
+          <t>34773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62868</t>
+          <t>63409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1117304</t>
+          <t>1117151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1135826</t>
+          <t>1135461</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>787858</t>
+          <t>788374</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>808286</t>
+          <t>808795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1912646</t>
+          <t>1912105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1940074</t>
+          <t>1940741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29797</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>30775</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56731</t>
+          <t>56987</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47404</t>
+          <t>47452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78444</t>
+          <t>78423</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>590909</t>
+          <t>591916</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608462</t>
+          <t>608423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>681513</t>
+          <t>681257</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>708476</t>
+          <t>707469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1280506</t>
+          <t>1280527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1311546</t>
+          <t>1311498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>6036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48458</t>
+          <t>48565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82100</t>
+          <t>82483</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49870</t>
+          <t>51417</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84470</t>
+          <t>84908</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281837</t>
+          <t>281109</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>999925</t>
+          <t>999542</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1033567</t>
+          <t>1033460</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1284700</t>
+          <t>1284262</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1319300</t>
+          <t>1317753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43620</t>
+          <t>41697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72099</t>
+          <t>70986</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>129765</t>
+          <t>130859</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180250</t>
+          <t>178281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>181613</t>
+          <t>183723</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242649</t>
+          <t>242144</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3313623</t>
+          <t>3314736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3342102</t>
+          <t>3344025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3351346</t>
+          <t>3353315</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3401831</t>
+          <t>3400737</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6674669</t>
+          <t>6675174</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6735705</t>
+          <t>6733595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido cinco o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14593</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>29385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25019</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46152</t>
+          <t>45059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>484815</t>
+          <t>484906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>496893</t>
+          <t>497120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>417561</t>
+          <t>418082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>432874</t>
+          <t>433227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>906527</t>
+          <t>907620</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>927660</t>
+          <t>926818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>14927</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28227</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52799</t>
+          <t>53131</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422052</t>
+          <t>422062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438438</t>
+          <t>438354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354353</t>
+          <t>353974</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367617</t>
+          <t>367653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>781994</t>
+          <t>781662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803309</t>
+          <t>803186</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>49780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15687</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28388</t>
+          <t>28822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>20552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>73847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>619371</t>
+          <t>618484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659575</t>
+          <t>659081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138523</t>
+          <t>138089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151224</t>
+          <t>151362</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>760206</t>
+          <t>761328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>813515</t>
+          <t>814623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48459</t>
+          <t>49284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74933</t>
+          <t>73865</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22786</t>
+          <t>24602</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64193</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75902</t>
+          <t>71840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127203</t>
+          <t>126676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>959886</t>
+          <t>960954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>986360</t>
+          <t>985535</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>913901</t>
+          <t>914130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>955308</t>
+          <t>953492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885709</t>
+          <t>1886236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1937010</t>
+          <t>1941072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>19872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36912</t>
+          <t>36696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>88188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>140474</t>
+          <t>141906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117010</t>
+          <t>120522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169921</t>
+          <t>170574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>438134</t>
+          <t>438350</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455153</t>
+          <t>455174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>700861</t>
+          <t>699429</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>756225</t>
+          <t>753147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1146460</t>
+          <t>1145807</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1199371</t>
+          <t>1195859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,84%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84206</t>
+          <t>83672</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113184</t>
+          <t>110978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86959</t>
+          <t>86330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117528</t>
+          <t>117226</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232106</t>
+          <t>232411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239060</t>
+          <t>239120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>648187</t>
+          <t>650393</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>677165</t>
+          <t>677699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>884350</t>
+          <t>884652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>914919</t>
+          <t>915548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116832</t>
+          <t>121876</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178213</t>
+          <t>179439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>266124</t>
+          <t>265691</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>361339</t>
+          <t>360498</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>413679</t>
+          <t>409606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>529892</t>
+          <t>518621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3197847</t>
+          <t>3196621</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3259228</t>
+          <t>3254184</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3216419</t>
+          <t>3217260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3311634</t>
+          <t>3312067</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6423926</t>
+          <t>6435197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6540139</t>
+          <t>6544212</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R3-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>13222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>458257</t>
+          <t>457650</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470906</t>
+          <t>470838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294775</t>
+          <t>293458</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304702</t>
+          <t>304711</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>758217</t>
+          <t>757899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773350</t>
+          <t>773639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>812</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>358707</t>
+          <t>359823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366109</t>
+          <t>366122</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365408</t>
+          <t>364959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>728246</t>
+          <t>729224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>737042</t>
+          <t>737823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>15851</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9832</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22366</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>528122</t>
+          <t>526538</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538893</t>
+          <t>538795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157950</t>
+          <t>157171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165997</t>
+          <t>165902</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>687805</t>
+          <t>688102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>703065</t>
+          <t>703146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14044</t>
+          <t>15107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32496</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>25298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>38740</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>27745</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>52314</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>38740</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>52736</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1205838</t>
+          <t>1204563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1224290</t>
+          <t>1223227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>688664</t>
+          <t>688987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>704162</t>
+          <t>704496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1878</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1913880</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1900306</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1924875</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>97,32%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>98,58%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1878</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1913880</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1899884</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1924705</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>15619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>20484</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29484</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335952</t>
+          <t>334936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>346665</t>
+          <t>346241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>548755</t>
+          <t>548268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>562652</t>
+          <t>562960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>889823</t>
+          <t>888888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>907278</t>
+          <t>906775</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34040</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60616</t>
+          <t>60614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33985</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61201</t>
+          <t>60041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1188144</t>
+          <t>1188146</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1214720</t>
+          <t>1215402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1485759</t>
+          <t>1486919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1512975</t>
+          <t>1513370</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36510</t>
+          <t>35839</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63511</t>
+          <t>63752</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>68943</t>
+          <t>68752</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106280</t>
+          <t>107790</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114070</t>
+          <t>113662</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160359</t>
+          <t>159238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3206679</t>
+          <t>3206438</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3233680</t>
+          <t>3234351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3271844</t>
+          <t>3270334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3309181</t>
+          <t>3309372</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6487955</t>
+          <t>6489076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6534244</t>
+          <t>6534652</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12557</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>14975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>23438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>424654</t>
+          <t>423032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436198</t>
+          <t>436189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298515</t>
+          <t>299479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311335</t>
+          <t>311308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>729201</t>
+          <t>728227</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745675</t>
+          <t>745530</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>9316</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26863</t>
+          <t>26531</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401559</t>
+          <t>399960</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415573</t>
+          <t>415482</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322799</t>
+          <t>323233</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>334063</t>
+          <t>334658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729945</t>
+          <t>730277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748517</t>
+          <t>747492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>32281</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>17833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41340</t>
+          <t>42499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598354</t>
+          <t>597134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>618824</t>
+          <t>618957</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243479</t>
+          <t>243385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255909</t>
+          <t>255923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848204</t>
+          <t>847045</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>871103</t>
+          <t>871711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>30426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>39315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35099</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61936</t>
+          <t>62141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128970</t>
+          <t>1128583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146241</t>
+          <t>1146535</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>729758</t>
+          <t>727342</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>749669</t>
+          <t>748765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1863731</t>
+          <t>1863526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1890568</t>
+          <t>1890507</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34954</t>
+          <t>33926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61956</t>
+          <t>62415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42471</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72549</t>
+          <t>72721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>493057</t>
+          <t>493514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>506250</t>
+          <t>506357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>699566</t>
+          <t>699107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>726568</t>
+          <t>727596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1199569</t>
+          <t>1199397</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1229647</t>
+          <t>1230478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61951</t>
+          <t>62885</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97233</t>
+          <t>98400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61677</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97687</t>
+          <t>98708</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1012118</t>
+          <t>1010951</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1047400</t>
+          <t>1046466</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1278546</t>
+          <t>1277525</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1314556</t>
+          <t>1313397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45406</t>
+          <t>45750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79910</t>
+          <t>82537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>150147</t>
+          <t>149462</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205507</t>
+          <t>203548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>205162</t>
+          <t>208719</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>271261</t>
+          <t>273997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3342000</t>
+          <t>3339373</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3376504</t>
+          <t>3376160</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3344618</t>
+          <t>3346577</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3399978</t>
+          <t>3400663</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6700774</t>
+          <t>6698038</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6766873</t>
+          <t>6763316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>14686</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>21770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414983</t>
+          <t>414406</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>426096</t>
+          <t>426500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>335398</t>
+          <t>335857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344978</t>
+          <t>345090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756700</t>
+          <t>754377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>770025</t>
+          <t>769843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,42 +6366,42 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6262</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2266</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12430</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6262</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2860</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13394</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>14979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370905</t>
+          <t>371294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,47 +6474,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>366011</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>359843</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>370007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>98,32%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>366011</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>358879</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>369413</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>735605</t>
+          <t>734521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746514</t>
+          <t>746254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24362</t>
+          <t>24613</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>509575</t>
+          <t>509475</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519866</t>
+          <t>519629</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148718</t>
+          <t>148443</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161583</t>
+          <t>161794</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663674</t>
+          <t>663423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>679755</t>
+          <t>679559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32487</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37502</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34773</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>61175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1117151</t>
+          <t>1117385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1135461</t>
+          <t>1135564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>788374</t>
+          <t>789302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>808795</t>
+          <t>808681</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1912105</t>
+          <t>1914339</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1940741</t>
+          <t>1940817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>13107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56987</t>
+          <t>56443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47452</t>
+          <t>47836</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78423</t>
+          <t>79162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>591916</t>
+          <t>590741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>608423</t>
+          <t>607599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>681257</t>
+          <t>681801</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>707469</t>
+          <t>707672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1280527</t>
+          <t>1279788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1311498</t>
+          <t>1311114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48565</t>
+          <t>50339</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82483</t>
+          <t>82266</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51417</t>
+          <t>49957</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84908</t>
+          <t>85861</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>280503</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>999542</t>
+          <t>999759</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1033460</t>
+          <t>1031686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1284262</t>
+          <t>1283309</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1317753</t>
+          <t>1319213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,35%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41697</t>
+          <t>42532</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70986</t>
+          <t>72722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130859</t>
+          <t>130474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>178281</t>
+          <t>182251</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>183723</t>
+          <t>183112</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242144</t>
+          <t>241727</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3314736</t>
+          <t>3313000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3344025</t>
+          <t>3343190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3353315</t>
+          <t>3349345</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3400737</t>
+          <t>3401122</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6675174</t>
+          <t>6675591</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6733595</t>
+          <t>6734206</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>22015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20786</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34188</t>
+          <t>38275</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>28799</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45059</t>
+          <t>50513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>491810</t>
+          <t>535587</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>484906</t>
+          <t>528603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>497120</t>
+          <t>541135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>426681</t>
+          <t>465167</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>418082</t>
+          <t>455766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433227</t>
+          <t>472413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>918491</t>
+          <t>1000754</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>907620</t>
+          <t>988516</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>926818</t>
+          <t>1010230</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13859</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30151</t>
+          <t>29610</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>16216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>43585</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31607</t>
+          <t>33980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>55927</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>431650</t>
+          <t>462099</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>422062</t>
+          <t>453602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438354</t>
+          <t>469295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>361835</t>
+          <t>400672</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353974</t>
+          <t>392152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367653</t>
+          <t>406927</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>793485</t>
+          <t>862770</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>781662</t>
+          <t>850428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803186</t>
+          <t>872375</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27990</t>
+          <t>30337</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>21350</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49780</t>
+          <t>41608</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>23015</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28822</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49032</t>
+          <t>53352</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20552</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73847</t>
+          <t>67690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>640274</t>
+          <t>441275</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618484</t>
+          <t>430004</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659081</t>
+          <t>450262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>145869</t>
+          <t>164482</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138089</t>
+          <t>156787</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151362</t>
+          <t>170607</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>786143</t>
+          <t>605757</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>761328</t>
+          <t>591419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>814623</t>
+          <t>616794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>60042</t>
+          <t>64130</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49284</t>
+          <t>51738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73865</t>
+          <t>78189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47020</t>
+          <t>51985</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>42055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63964</t>
+          <t>64016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>107062</t>
+          <t>116115</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71840</t>
+          <t>99466</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126676</t>
+          <t>133494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>974777</t>
+          <t>1067713</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>960954</t>
+          <t>1053654</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>985535</t>
+          <t>1080105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>931074</t>
+          <t>809226</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>914130</t>
+          <t>797195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>953492</t>
+          <t>819156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1905850</t>
+          <t>1876939</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1886236</t>
+          <t>1859560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1941072</t>
+          <t>1893588</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27131</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19872</t>
+          <t>20716</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36696</t>
+          <t>38774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>117882</t>
+          <t>123820</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>88188</t>
+          <t>108448</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>141906</t>
+          <t>139214</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>145012</t>
+          <t>152432</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120522</t>
+          <t>135267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170574</t>
+          <t>173031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>447915</t>
+          <t>539351</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>438350</t>
+          <t>529190</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455174</t>
+          <t>547248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>723453</t>
+          <t>707030</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>699429</t>
+          <t>691636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>753147</t>
+          <t>722402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1171369</t>
+          <t>1246382</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1145807</t>
+          <t>1225783</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1195859</t>
+          <t>1263547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,33%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>97265</t>
+          <t>106478</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83672</t>
+          <t>92514</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>110978</t>
+          <t>122297</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>100907</t>
+          <t>110112</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86330</t>
+          <t>93923</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117226</t>
+          <t>126183</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236865</t>
+          <t>233594</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232411</t>
+          <t>229036</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239120</t>
+          <t>235768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>664106</t>
+          <t>737803</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>650393</t>
+          <t>721984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>677699</t>
+          <t>751767</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>900971</t>
+          <t>971397</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>884652</t>
+          <t>955326</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>915548</t>
+          <t>987586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>152769</t>
+          <t>162858</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121876</t>
+          <t>142188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>179439</t>
+          <t>186390</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>324741</t>
+          <t>351011</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>265691</t>
+          <t>323660</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>360498</t>
+          <t>378936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>477510</t>
+          <t>513870</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>409606</t>
+          <t>479344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>518621</t>
+          <t>548383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3223291</t>
+          <t>3279618</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3196621</t>
+          <t>3256086</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3254184</t>
+          <t>3300288</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3253017</t>
+          <t>3284382</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3217260</t>
+          <t>3256457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3312067</t>
+          <t>3311733</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6476308</t>
+          <t>6563999</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6435197</t>
+          <t>6529486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6544212</t>
+          <t>6598525</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
